--- a/artfynd/A 2238-2025 artfynd.xlsx
+++ b/artfynd/A 2238-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122325159</v>
       </c>
       <c r="B2" t="n">
-        <v>97129</v>
+        <v>97139</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 2238-2025 artfynd.xlsx
+++ b/artfynd/A 2238-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122325159</v>
       </c>
       <c r="B2" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 2238-2025 artfynd.xlsx
+++ b/artfynd/A 2238-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122325159</v>
       </c>
       <c r="B2" t="n">
-        <v>97151</v>
+        <v>97156</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 2238-2025 artfynd.xlsx
+++ b/artfynd/A 2238-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>122325159</v>
       </c>
       <c r="B2" t="n">
-        <v>97156</v>
+        <v>97165</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>221945</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -789,6 +784,259 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122540874</v>
+      </c>
+      <c r="B3" t="n">
+        <v>94829</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>210</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>697558</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6556314</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Vid basen av rötbruten grov gran.</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies # Vid basen av rötbruten grov gran.</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122540873</v>
+      </c>
+      <c r="B4" t="n">
+        <v>94733</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2818</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>697558</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6556314</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Vid basen av rötbruten grov gran.</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies # Vid basen av rötbruten grov gran.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2238-2025 artfynd.xlsx
+++ b/artfynd/A 2238-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>122325159</v>
       </c>
       <c r="B2" t="n">
-        <v>97165</v>
+        <v>97178</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>221945</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -789,7 +794,7 @@
         <v>122540874</v>
       </c>
       <c r="B3" t="n">
-        <v>94829</v>
+        <v>94842</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,6 +809,11 @@
       <c r="E3" t="n">
         <v>210</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Buxbaumia viridis</t>
@@ -886,6 +896,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
@@ -920,7 +935,7 @@
         <v>122540873</v>
       </c>
       <c r="B4" t="n">
-        <v>94733</v>
+        <v>94746</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,6 +950,11 @@
       <c r="E4" t="n">
         <v>2818</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Herzogiella seligeri</t>
@@ -1009,6 +1029,11 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK4" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -1036,6 +1061,127 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122325011</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91037</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1618</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hängticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Postia ceriflua</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kvarnbacken, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>697550</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6556314</v>
+      </c>
+      <c r="S5" t="n">
+        <v>13</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På rötbruten stubbe av gran. Flera fruktkroppar.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2238-2025 artfynd.xlsx
+++ b/artfynd/A 2238-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122325159</v>
       </c>
       <c r="B2" t="n">
-        <v>97178</v>
+        <v>97191</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>122540874</v>
       </c>
       <c r="B3" t="n">
-        <v>94842</v>
+        <v>94855</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>122540873</v>
       </c>
       <c r="B4" t="n">
-        <v>94746</v>
+        <v>94759</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>122325011</v>
       </c>
       <c r="B5" t="n">
-        <v>91037</v>
+        <v>91050</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 2238-2025 artfynd.xlsx
+++ b/artfynd/A 2238-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122540874</v>
+        <v>122540873</v>
       </c>
       <c r="B3" t="n">
-        <v>94855</v>
+        <v>94759</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,33 +807,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
@@ -932,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122540873</v>
+        <v>122540874</v>
       </c>
       <c r="B4" t="n">
-        <v>94759</v>
+        <v>94855</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,24 +939,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Emilia Blixt, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 2238-2025 artfynd.xlsx
+++ b/artfynd/A 2238-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122325159</v>
       </c>
       <c r="B2" t="n">
-        <v>97191</v>
+        <v>97194</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>122540873</v>
       </c>
       <c r="B3" t="n">
-        <v>94759</v>
+        <v>94761</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>122540874</v>
       </c>
       <c r="B4" t="n">
-        <v>94855</v>
+        <v>94857</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>122325011</v>
       </c>
       <c r="B5" t="n">
-        <v>91050</v>
+        <v>91051</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 2238-2025 artfynd.xlsx
+++ b/artfynd/A 2238-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122325159</v>
       </c>
       <c r="B2" t="n">
-        <v>97194</v>
+        <v>97195</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>122540873</v>
       </c>
       <c r="B3" t="n">
-        <v>94761</v>
+        <v>94762</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>122540874</v>
       </c>
       <c r="B4" t="n">
-        <v>94857</v>
+        <v>94858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>122325011</v>
       </c>
       <c r="B5" t="n">
-        <v>91051</v>
+        <v>91052</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 2238-2025 artfynd.xlsx
+++ b/artfynd/A 2238-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122325159</v>
       </c>
       <c r="B2" t="n">
-        <v>97195</v>
+        <v>97198</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122540873</v>
+        <v>122540874</v>
       </c>
       <c r="B3" t="n">
-        <v>94762</v>
+        <v>94861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,24 +807,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
@@ -923,10 +932,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122540874</v>
+        <v>122540873</v>
       </c>
       <c r="B4" t="n">
-        <v>94858</v>
+        <v>94765</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,33 +948,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
@@ -1067,7 +1067,7 @@
         <v>122325011</v>
       </c>
       <c r="B5" t="n">
-        <v>91052</v>
+        <v>91055</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 2238-2025 artfynd.xlsx
+++ b/artfynd/A 2238-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122540874</v>
+        <v>122540873</v>
       </c>
       <c r="B3" t="n">
-        <v>94861</v>
+        <v>94765</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,33 +807,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
@@ -932,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122540873</v>
+        <v>122540874</v>
       </c>
       <c r="B4" t="n">
-        <v>94765</v>
+        <v>94861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,24 +939,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>

--- a/artfynd/A 2238-2025 artfynd.xlsx
+++ b/artfynd/A 2238-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122540873</v>
+        <v>122540874</v>
       </c>
       <c r="B3" t="n">
-        <v>94765</v>
+        <v>94964</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,24 +807,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
@@ -923,10 +932,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122540874</v>
+        <v>122540873</v>
       </c>
       <c r="B4" t="n">
-        <v>94861</v>
+        <v>94868</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,33 +948,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
@@ -1067,7 +1067,7 @@
         <v>122325011</v>
       </c>
       <c r="B5" t="n">
-        <v>91055</v>
+        <v>91158</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 2238-2025 artfynd.xlsx
+++ b/artfynd/A 2238-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>122540874</v>
       </c>
       <c r="B3" t="n">
-        <v>94964</v>
+        <v>94972</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>122540873</v>
       </c>
       <c r="B4" t="n">
-        <v>94868</v>
+        <v>94876</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>122325011</v>
       </c>
       <c r="B5" t="n">
-        <v>91158</v>
+        <v>91162</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 2238-2025 artfynd.xlsx
+++ b/artfynd/A 2238-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122540874</v>
+        <v>122540873</v>
       </c>
       <c r="B3" t="n">
-        <v>94972</v>
+        <v>94878</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,33 +807,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
@@ -932,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122540873</v>
+        <v>122540874</v>
       </c>
       <c r="B4" t="n">
-        <v>94876</v>
+        <v>94974</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,24 +939,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>

--- a/artfynd/A 2238-2025 artfynd.xlsx
+++ b/artfynd/A 2238-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122540873</v>
+        <v>122540874</v>
       </c>
       <c r="B3" t="n">
-        <v>94878</v>
+        <v>94974</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,24 +807,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
@@ -923,10 +932,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122540874</v>
+        <v>122540873</v>
       </c>
       <c r="B4" t="n">
-        <v>94974</v>
+        <v>94878</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,33 +948,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
